--- a/features/quotation/data/Attractions.xlsx
+++ b/features/quotation/data/Attractions.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHAKH NAIR\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78E40CD-84FA-4D3F-B75A-E25025064171}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{737634F9-4430-4482-8CBA-574755DBC79D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{440128AA-9F10-42BF-BF5F-9CF7A067EEF0}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="1051">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2708" uniqueCount="1096">
   <si>
     <t>City</t>
   </si>
@@ -3231,7 +3231,153 @@
     <t xml:space="preserve">KOH TAO &amp; KOH NANGYUAN BY SPEED BOAT ( EX. NPF ) </t>
   </si>
   <si>
-    <t xml:space="preserve">Yona Beach Club - Morning Pool Sofa (2 Pax)                           </t>
+    <t>Phuket FantaSea - Show + Buffet Dinner</t>
+  </si>
+  <si>
+    <t>Phuket FantaSea - Show Only</t>
+  </si>
+  <si>
+    <t>Fantasea Show</t>
+  </si>
+  <si>
+    <t>Phuket Carnival Magic - Show + Buffet Dinner</t>
+  </si>
+  <si>
+    <t>Phuket Carnival Magic - Show Only</t>
+  </si>
+  <si>
+    <t>Carnival Magic</t>
+  </si>
+  <si>
+    <t>Guide Sai</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Golden Buddha + Marble Buddha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Golden Buddha + Wat Pho Reclining Buddha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Golden Buddha + Mini Reclining Buddha Wat Mahapruettharam </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Golden Buddha + Marble Buddha + Mini Reclining Buddha Wat Mahapruettharam </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Golden Buddha + Marble Buddha + Wat Pho Reclining Buddha </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Marble Buddha + Wat Pho Reclining Buddha </t>
+  </si>
+  <si>
+    <t>Guide Sai - Marble Buddha + Mini Reclining Buddha Wat Mahapruettharam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Grand Palace + Emerald Buddha </t>
+  </si>
+  <si>
+    <t>Guide Sai - Wat Arun Temple of Dawn</t>
+  </si>
+  <si>
+    <t>Guide Sai - Grand Palace + Emerald Buddha + Wat Pho Reclining Buddha</t>
+  </si>
+  <si>
+    <t>Guide Sai - Grand Palace + Emerald Buddha +Golden Buddha + Marble Buddha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Grand Palace + Emerald Buddha +Golden Buddha + Marble Buddha + Wat Pho Reclining Buddha </t>
+  </si>
+  <si>
+    <t>Guide Sai - Half Day Tours Damnoen Saduak Floating Market</t>
+  </si>
+  <si>
+    <t>Guide Sai - Full Day Tours Damnoen Saduak Floating Market</t>
+  </si>
+  <si>
+    <t>Guide Sai - Amphawa Floating Market ( Wat Bang Kung - Maeklong Railway Market + Fire Flies )</t>
+  </si>
+  <si>
+    <t>Guide Sai - Ayuthaya Full Day Tour</t>
+  </si>
+  <si>
+    <t>Guide Sai - Kanjanaburi River Kwai Bridge+ Cemetery - 6 Hours</t>
+  </si>
+  <si>
+    <t>Guide Sai - Kanjanaburi River Kwai Bridge+ Krasae Cave  - 9 Hours</t>
+  </si>
+  <si>
+    <t>Guide Sai - Kanjanaburi River Kwai Bridge+ Krasae Cave+Erawan Waterfall - 12 Hours</t>
+  </si>
+  <si>
+    <t>Guide Sai - Ancient City</t>
+  </si>
+  <si>
+    <t>Guide Sai - Erawan Museum</t>
+  </si>
+  <si>
+    <t>Guide Sai - Ancient City + Erawan Museum</t>
+  </si>
+  <si>
+    <t>Guide Sai - Safari World</t>
+  </si>
+  <si>
+    <t>Golden Buddha Ticket Price - Wat Tramit</t>
+  </si>
+  <si>
+    <t>Marble Buddha Ticket Price - Wat Benchamabophit</t>
+  </si>
+  <si>
+    <t>Reclining Buddha Ticket Price - Wat Pho</t>
+  </si>
+  <si>
+    <t>Mini Reclining Buddha Ticket Price</t>
+  </si>
+  <si>
+    <t>Wat Arun Ticket Price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boat From Wat Pho to Wat Arun </t>
+  </si>
+  <si>
+    <t>Bangkok Temples</t>
+  </si>
+  <si>
+    <t>Ayuthaya Temples</t>
+  </si>
+  <si>
+    <t>Wat Mahathat</t>
+  </si>
+  <si>
+    <t>Wat Phra Si Sanphet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Wat Chaiwatthanaram </t>
+  </si>
+  <si>
+    <t>Wat Yai Chai Mongkhon</t>
+  </si>
+  <si>
+    <t>Wat Phanan Choeng</t>
+  </si>
+  <si>
+    <t>Grand Palace + Emerald Buddha Ticket Price</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Yona Beach Club - Morning Pool Sofa (2 Pax)                             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Aptos"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Guide Sai - Grand Palace + Emerald Buddha + Wat Arun Temple of Dawn                                         </t>
   </si>
 </sst>
 </file>
@@ -8644,9 +8790,7 @@
       <c r="B222" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="C222" s="4">
-        <v>0</v>
-      </c>
+      <c r="C222" s="4"/>
       <c r="D222" s="4">
         <v>250</v>
       </c>
@@ -13668,7 +13812,7 @@
         <v>384</v>
       </c>
       <c r="B484" s="5" t="s">
-        <v>1050</v>
+        <v>1094</v>
       </c>
       <c r="C484" s="6">
         <v>6800</v>
@@ -17245,324 +17389,700 @@
       </c>
     </row>
     <row r="669" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A669" s="3"/>
-      <c r="B669" s="3"/>
-      <c r="C669" s="4"/>
-      <c r="D669" s="4"/>
+      <c r="A669" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B669" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="C669" s="4">
+        <v>1650</v>
+      </c>
+      <c r="D669" s="4">
+        <v>1500</v>
+      </c>
       <c r="E669" s="4"/>
-      <c r="F669" s="3"/>
+      <c r="F669" s="3" t="s">
+        <v>1052</v>
+      </c>
     </row>
     <row r="670" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A670" s="3"/>
-      <c r="B670" s="3"/>
-      <c r="C670" s="4"/>
-      <c r="D670" s="4"/>
+      <c r="A670" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B670" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="C670" s="4">
+        <v>1450</v>
+      </c>
+      <c r="D670" s="4">
+        <v>1450</v>
+      </c>
       <c r="E670" s="4"/>
-      <c r="F670" s="3"/>
+      <c r="F670" s="3" t="s">
+        <v>1052</v>
+      </c>
     </row>
     <row r="671" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A671" s="3"/>
-      <c r="B671" s="3"/>
-      <c r="C671" s="4"/>
-      <c r="D671" s="4"/>
+      <c r="A671" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B671" s="3" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C671" s="4">
+        <v>1750</v>
+      </c>
+      <c r="D671" s="4">
+        <v>1650</v>
+      </c>
       <c r="E671" s="4"/>
-      <c r="F671" s="3"/>
+      <c r="F671" s="3" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="672" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A672" s="3"/>
-      <c r="B672" s="3"/>
-      <c r="C672" s="4"/>
-      <c r="D672" s="4"/>
+      <c r="A672" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B672" s="3" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C672" s="4">
+        <v>1550</v>
+      </c>
+      <c r="D672" s="4">
+        <v>1550</v>
+      </c>
       <c r="E672" s="4"/>
-      <c r="F672" s="3"/>
+      <c r="F672" s="3" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="673" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A673" s="3"/>
-      <c r="B673" s="3"/>
-      <c r="C673" s="4"/>
+      <c r="A673" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B673" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="C673" s="4">
+        <v>600</v>
+      </c>
       <c r="D673" s="4"/>
       <c r="E673" s="4"/>
-      <c r="F673" s="3"/>
+      <c r="F673" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="674" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A674" s="3"/>
-      <c r="B674" s="3"/>
-      <c r="C674" s="4"/>
+      <c r="A674" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B674" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C674" s="4">
+        <v>1000</v>
+      </c>
       <c r="D674" s="4"/>
       <c r="E674" s="4"/>
-      <c r="F674" s="3"/>
+      <c r="F674" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="675" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A675" s="3"/>
-      <c r="B675" s="3"/>
-      <c r="C675" s="4"/>
+      <c r="A675" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B675" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="C675" s="4">
+        <v>600</v>
+      </c>
       <c r="D675" s="4"/>
       <c r="E675" s="4"/>
-      <c r="F675" s="3"/>
+      <c r="F675" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="676" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A676" s="3"/>
-      <c r="B676" s="3"/>
-      <c r="C676" s="4"/>
+      <c r="A676" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B676" s="5" t="s">
+        <v>1060</v>
+      </c>
+      <c r="C676" s="4">
+        <v>1000</v>
+      </c>
       <c r="D676" s="4"/>
       <c r="E676" s="4"/>
-      <c r="F676" s="3"/>
+      <c r="F676" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="677" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A677" s="3"/>
-      <c r="B677" s="3"/>
-      <c r="C677" s="4"/>
+      <c r="A677" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B677" s="5" t="s">
+        <v>1061</v>
+      </c>
+      <c r="C677" s="4">
+        <v>1200</v>
+      </c>
       <c r="D677" s="4"/>
       <c r="E677" s="4"/>
-      <c r="F677" s="3"/>
+      <c r="F677" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="678" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A678" s="3"/>
-      <c r="B678" s="3"/>
-      <c r="C678" s="4"/>
+      <c r="A678" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B678" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C678" s="4">
+        <v>1000</v>
+      </c>
       <c r="D678" s="4"/>
       <c r="E678" s="4"/>
-      <c r="F678" s="3"/>
+      <c r="F678" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="679" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A679" s="3"/>
-      <c r="B679" s="3"/>
-      <c r="C679" s="4"/>
+      <c r="A679" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B679" s="5" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C679" s="4">
+        <v>700</v>
+      </c>
       <c r="D679" s="4"/>
       <c r="E679" s="4"/>
-      <c r="F679" s="3"/>
+      <c r="F679" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="680" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A680" s="3"/>
-      <c r="B680" s="3"/>
-      <c r="C680" s="4"/>
+      <c r="A680" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B680" s="5" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C680" s="4">
+        <v>1000</v>
+      </c>
       <c r="D680" s="4"/>
       <c r="E680" s="4"/>
-      <c r="F680" s="3"/>
+      <c r="F680" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="681" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A681" s="3"/>
-      <c r="B681" s="3"/>
-      <c r="C681" s="4"/>
+      <c r="A681" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B681" s="5" t="s">
+        <v>1065</v>
+      </c>
+      <c r="C681" s="4">
+        <v>800</v>
+      </c>
       <c r="D681" s="4"/>
       <c r="E681" s="4"/>
-      <c r="F681" s="3"/>
+      <c r="F681" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="682" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A682" s="3"/>
-      <c r="B682" s="3"/>
-      <c r="C682" s="4"/>
+      <c r="A682" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B682" s="5" t="s">
+        <v>1095</v>
+      </c>
+      <c r="C682" s="4">
+        <v>1200</v>
+      </c>
       <c r="D682" s="4"/>
       <c r="E682" s="4"/>
-      <c r="F682" s="3"/>
+      <c r="F682" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="683" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A683" s="3"/>
-      <c r="B683" s="3"/>
-      <c r="C683" s="4"/>
+      <c r="A683" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B683" s="5" t="s">
+        <v>1066</v>
+      </c>
+      <c r="C683" s="4">
+        <v>1200</v>
+      </c>
       <c r="D683" s="4"/>
       <c r="E683" s="4"/>
-      <c r="F683" s="3"/>
+      <c r="F683" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="684" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A684" s="3"/>
-      <c r="B684" s="3"/>
-      <c r="C684" s="4"/>
+      <c r="A684" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B684" s="5" t="s">
+        <v>1067</v>
+      </c>
+      <c r="C684" s="4">
+        <v>1400</v>
+      </c>
       <c r="D684" s="4"/>
       <c r="E684" s="4"/>
-      <c r="F684" s="3"/>
+      <c r="F684" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="685" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A685" s="3"/>
-      <c r="B685" s="3"/>
-      <c r="C685" s="4"/>
+      <c r="A685" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B685" s="5" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C685" s="4">
+        <v>2000</v>
+      </c>
       <c r="D685" s="4"/>
       <c r="E685" s="4"/>
-      <c r="F685" s="3"/>
+      <c r="F685" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="686" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A686" s="3"/>
-      <c r="B686" s="3"/>
-      <c r="C686" s="4"/>
+      <c r="A686" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B686" s="5" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C686" s="4">
+        <v>1200</v>
+      </c>
       <c r="D686" s="4"/>
       <c r="E686" s="4"/>
-      <c r="F686" s="3"/>
+      <c r="F686" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="687" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A687" s="3"/>
-      <c r="B687" s="3"/>
-      <c r="C687" s="4"/>
+      <c r="A687" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B687" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C687" s="4">
+        <v>1500</v>
+      </c>
       <c r="D687" s="4"/>
       <c r="E687" s="4"/>
-      <c r="F687" s="3"/>
+      <c r="F687" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="688" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A688" s="3"/>
-      <c r="B688" s="3"/>
-      <c r="C688" s="4"/>
+      <c r="A688" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B688" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="C688" s="4">
+        <v>2000</v>
+      </c>
       <c r="D688" s="4"/>
       <c r="E688" s="4"/>
-      <c r="F688" s="3"/>
+      <c r="F688" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="689" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A689" s="3"/>
-      <c r="B689" s="3"/>
-      <c r="C689" s="4"/>
+      <c r="A689" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B689" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="C689" s="4">
+        <v>1500</v>
+      </c>
       <c r="D689" s="4"/>
       <c r="E689" s="4"/>
-      <c r="F689" s="3"/>
+      <c r="F689" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="690" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A690" s="3"/>
-      <c r="B690" s="3"/>
-      <c r="C690" s="4"/>
+      <c r="A690" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B690" s="5" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C690" s="4">
+        <v>1500</v>
+      </c>
       <c r="D690" s="4"/>
       <c r="E690" s="4"/>
-      <c r="F690" s="3"/>
+      <c r="F690" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="691" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A691" s="3"/>
-      <c r="B691" s="3"/>
-      <c r="C691" s="4"/>
+      <c r="A691" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B691" s="5" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C691" s="4">
+        <v>1800</v>
+      </c>
       <c r="D691" s="4"/>
       <c r="E691" s="4"/>
-      <c r="F691" s="3"/>
+      <c r="F691" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="692" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A692" s="3"/>
-      <c r="B692" s="3"/>
-      <c r="C692" s="4"/>
+      <c r="A692" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B692" s="5" t="s">
+        <v>1075</v>
+      </c>
+      <c r="C692" s="4">
+        <v>2500</v>
+      </c>
       <c r="D692" s="4"/>
       <c r="E692" s="4"/>
-      <c r="F692" s="3"/>
+      <c r="F692" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="693" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A693" s="3"/>
-      <c r="B693" s="3"/>
-      <c r="C693" s="4"/>
+      <c r="A693" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B693" s="5" t="s">
+        <v>1076</v>
+      </c>
+      <c r="C693" s="4">
+        <v>1200</v>
+      </c>
       <c r="D693" s="4"/>
       <c r="E693" s="4"/>
-      <c r="F693" s="3"/>
+      <c r="F693" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="694" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A694" s="3"/>
-      <c r="B694" s="3"/>
-      <c r="C694" s="4"/>
+      <c r="A694" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B694" s="5" t="s">
+        <v>1077</v>
+      </c>
+      <c r="C694" s="4">
+        <v>1500</v>
+      </c>
       <c r="D694" s="4"/>
       <c r="E694" s="4"/>
-      <c r="F694" s="3"/>
+      <c r="F694" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="695" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A695" s="3"/>
-      <c r="B695" s="3"/>
-      <c r="C695" s="4"/>
+      <c r="A695" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B695" s="5" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C695" s="4">
+        <v>1500</v>
+      </c>
       <c r="D695" s="4"/>
       <c r="E695" s="4"/>
-      <c r="F695" s="3"/>
+      <c r="F695" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="696" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A696" s="3"/>
-      <c r="B696" s="3"/>
-      <c r="C696" s="4"/>
+      <c r="A696" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B696" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="C696" s="4">
+        <v>1000</v>
+      </c>
       <c r="D696" s="4"/>
       <c r="E696" s="4"/>
-      <c r="F696" s="3"/>
+      <c r="F696" s="3" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="697" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A697" s="3"/>
-      <c r="B697" s="3"/>
-      <c r="C697" s="4"/>
-      <c r="D697" s="4"/>
-      <c r="E697" s="4"/>
-      <c r="F697" s="3"/>
+      <c r="A697" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B697" s="3" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C697" s="4">
+        <v>100</v>
+      </c>
+      <c r="D697" s="4">
+        <v>100</v>
+      </c>
+      <c r="E697" s="4">
+        <v>100</v>
+      </c>
+      <c r="F697" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="698" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A698" s="3"/>
-      <c r="B698" s="3"/>
-      <c r="C698" s="4"/>
-      <c r="D698" s="4"/>
-      <c r="E698" s="4"/>
-      <c r="F698" s="3"/>
+      <c r="A698" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B698" s="3" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C698" s="4">
+        <v>100</v>
+      </c>
+      <c r="D698" s="4">
+        <v>100</v>
+      </c>
+      <c r="E698" s="4">
+        <v>100</v>
+      </c>
+      <c r="F698" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="699" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A699" s="3"/>
-      <c r="B699" s="3"/>
-      <c r="C699" s="4"/>
-      <c r="D699" s="4"/>
-      <c r="E699" s="4"/>
-      <c r="F699" s="3"/>
+      <c r="A699" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B699" s="3" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C699" s="4">
+        <v>300</v>
+      </c>
+      <c r="D699" s="4">
+        <v>300</v>
+      </c>
+      <c r="E699" s="4">
+        <v>300</v>
+      </c>
+      <c r="F699" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="700" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A700" s="3"/>
-      <c r="B700" s="3"/>
-      <c r="C700" s="4"/>
-      <c r="D700" s="4"/>
-      <c r="E700" s="4"/>
-      <c r="F700" s="3"/>
+      <c r="A700" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B700" s="3" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C700" s="4">
+        <v>40</v>
+      </c>
+      <c r="D700" s="4">
+        <v>40</v>
+      </c>
+      <c r="E700" s="4">
+        <v>40</v>
+      </c>
+      <c r="F700" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="701" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A701" s="3"/>
-      <c r="B701" s="3"/>
-      <c r="C701" s="4"/>
-      <c r="D701" s="4"/>
-      <c r="E701" s="4"/>
-      <c r="F701" s="3"/>
+      <c r="A701" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B701" s="3" t="s">
+        <v>1084</v>
+      </c>
+      <c r="C701" s="4">
+        <v>200</v>
+      </c>
+      <c r="D701" s="4">
+        <v>200</v>
+      </c>
+      <c r="E701" s="4">
+        <v>200</v>
+      </c>
+      <c r="F701" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="702" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A702" s="3"/>
-      <c r="B702" s="3"/>
-      <c r="C702" s="4"/>
-      <c r="D702" s="4"/>
-      <c r="E702" s="4"/>
-      <c r="F702" s="3"/>
+      <c r="A702" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B702" s="3" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C702" s="4">
+        <v>500</v>
+      </c>
+      <c r="D702" s="4">
+        <v>500</v>
+      </c>
+      <c r="E702" s="4">
+        <v>500</v>
+      </c>
+      <c r="F702" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="703" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A703" s="3"/>
-      <c r="B703" s="3"/>
-      <c r="C703" s="4"/>
-      <c r="D703" s="4"/>
-      <c r="E703" s="4"/>
-      <c r="F703" s="3"/>
+      <c r="A703" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B703" s="3" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C703" s="4">
+        <v>5</v>
+      </c>
+      <c r="D703" s="4">
+        <v>5</v>
+      </c>
+      <c r="E703" s="4">
+        <v>5</v>
+      </c>
+      <c r="F703" s="3" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="704" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A704" s="3"/>
-      <c r="B704" s="3"/>
-      <c r="C704" s="4"/>
-      <c r="D704" s="4"/>
-      <c r="E704" s="4"/>
-      <c r="F704" s="3"/>
+      <c r="A704" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B704" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C704" s="4">
+        <v>80</v>
+      </c>
+      <c r="D704" s="4">
+        <v>80</v>
+      </c>
+      <c r="E704" s="4">
+        <v>80</v>
+      </c>
+      <c r="F704" s="3" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="705" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A705" s="3"/>
-      <c r="B705" s="3"/>
-      <c r="C705" s="4"/>
-      <c r="D705" s="4"/>
-      <c r="E705" s="4"/>
-      <c r="F705" s="3"/>
+      <c r="A705" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B705" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="C705" s="4">
+        <v>80</v>
+      </c>
+      <c r="D705" s="4">
+        <v>80</v>
+      </c>
+      <c r="E705" s="4">
+        <v>80</v>
+      </c>
+      <c r="F705" s="3" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="706" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A706" s="3"/>
-      <c r="B706" s="3"/>
-      <c r="C706" s="4"/>
-      <c r="D706" s="4"/>
-      <c r="E706" s="4"/>
-      <c r="F706" s="3"/>
+      <c r="A706" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B706" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C706" s="4">
+        <v>80</v>
+      </c>
+      <c r="D706" s="4">
+        <v>80</v>
+      </c>
+      <c r="E706" s="4">
+        <v>80</v>
+      </c>
+      <c r="F706" s="3" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="707" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A707" s="3"/>
-      <c r="B707" s="3"/>
-      <c r="C707" s="4"/>
-      <c r="D707" s="4"/>
-      <c r="E707" s="4"/>
-      <c r="F707" s="3"/>
+      <c r="A707" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B707" s="3" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C707" s="4">
+        <v>20</v>
+      </c>
+      <c r="D707" s="4">
+        <v>20</v>
+      </c>
+      <c r="E707" s="4">
+        <v>20</v>
+      </c>
+      <c r="F707" s="3" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="708" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A708" s="3"/>
-      <c r="B708" s="3"/>
-      <c r="C708" s="4"/>
-      <c r="D708" s="4"/>
-      <c r="E708" s="4"/>
-      <c r="F708" s="3"/>
+      <c r="A708" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B708" s="3" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C708" s="4">
+        <v>20</v>
+      </c>
+      <c r="D708" s="4">
+        <v>20</v>
+      </c>
+      <c r="E708" s="4">
+        <v>20</v>
+      </c>
+      <c r="F708" s="3" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="709" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A709" s="3"/>
